--- a/data_extactor/batch_10_fa/batch_0089_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0089_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | ترتیب‌دهی اطلاعات | چالاکی دست | توجه شنیداری | بینایی نزدیک | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | چالاکی انگشتان | توجه انتخابی | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | تجسم | وضوح گفتار | درک عمق | کنترل سرعت | جهت‌گیری پاسخ</t>
+          <t>ثبات دست و بازو | ترتیب‌دهی اطلاعات | مهارت دستی | توجه شنیداری | بینایی نزدیک | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | توجه انتخابی | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | تجسم | وضوح گفتار | درک عمق | کنترل نرخ | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سپری کردن زمان در حالت ایستاده | اهمیت دقیق یا درست بودن | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | سپری کردن زمان در حال راه رفتن یا دویدن | کار با یا کمک به یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین چسب‌زنی | برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اره‌کاری چوب | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین کفش‌دوزی | تیزکنندگان ابزار، سوهان‌کاران و اره‌تیزکن‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | هماهنگی چند عضو | چالاکی دست | قدرت تنه | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله | درک شفاهی | توجه شنیداری | زمان عکس‌العمل | تجسم | بیان شفاهی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | قدرت تنه | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله | درک شفاهی | توجه شنیداری | زمان عکس‌العمل | تجسم | بیان شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | سپری کردن زمان در حالت ایستاده | اهمیت دقیق یا درست بودن | سپری کردن زمان در حال راه رفتن یا دویدن | آزادی در تصمیم‌گیری | ارتباط با دیگران | کار با یا کمک به یک گروه کاری یا تیم | داخل ساختمان، با کنترل شرایط محیطی | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | سپری کردن زمان برای انجام حرکات تکراری</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین چسب‌زنی | برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین کالاهای کاغذی | کارگران صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین نورد فلز و پلاستیک | دوزندگان دستی | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین کفش‌دوزی | اپراتورها و متصدیان ماشین سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | پایش | تفکر انتقادی | گوش‌دادن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | امور اداری و مدیریت | مکانیک | امنیت و ایمنی عمومی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | چالاکی انگشتان | چالاکی دست | زمان عکس‌العمل | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | انعطاف‌پذیری گسترده | قدرت ایستا | توجه انتخابی | حساسیت به مسئله | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | وضوح گفتار | توجه شنیداری | تشخیص رنگ‌های بصری | بینایی دور | سرعت مچ و انگشت | کنترل سرعت</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | زمان عکس‌العمل | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | توجه انتخابی | حساسیت به مسئله | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | وضوح گفتار | توجه شنیداری | تشخیص رنگ بصری | بینایی دور | سرعت مچ و انگشتان | کنترل نرخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>سپری کردن زمان در حال راه رفتن یا دویدن | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سپری کردن زمان در حالت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش, کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | سپری کردن زمان برای انجام حرکات تکراری | کار با یا کمک به یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی</t>
+          <t>صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین چسب‌زنی | بوبین‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش و ورق‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و کشش فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین نورد فلز و پلاستیک | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین کفش‌دوزی | اپراتورها و متصدیان ماشین سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | بینایی نزدیک | چالاکی انگشتان | ثبات دست و بازو | درک شفاهی | چالاکی دست | هماهنگی چند عضو | زمان عکس‌العمل | کنترل سرعت | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | اشتراک زمانی | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | توجه شنیداری</t>
+          <t>حساسیت به مسئله | دقت کنترل | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | درک شفاهی | مهارت دستی | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | تقسیم توجه | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | کار با یا کمک به یک گروه کاری یا تیم | داخل ساختمان، با کنترل شرایط محیطی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | دفعات تصمیم‌گیری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین چسب‌زنی | بوبین‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش و ورق‌کن | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین اکستروژن و کشش فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین قالب‌سازی، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش‌دادن فعال | درک مطلب | سخن‌گفتن | ریاضیات | یادگیری فعال | پایش | استراتژی‌های یادگیری | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>تجسم | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال ریاضی | درک کتبی | بیان شفاهی | چالاکی انگشتان | سهولت کار با اعداد | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | سرعت ادراکی | توجه انتخابی | روان بودن ایده‌ها | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | بینایی دور | چالاکی دست | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تشخیص رنگ‌های بصری | دقت کنترل | اشتراک زمانی</t>
+          <t>تجسم | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال ریاضی | درک کتبی | بیان شفاهی | مهارت انگشتان | توانایی عددی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | سرعت ادراکی | توجه انتخابی | روانی ایده‌ها | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | بینایی دور | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا کمک به یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | دفعات تصمیم‌گیری | فشار زمانی | مکالمات تلفنی | داخل ساختمان، با کنترل شرایط محیطی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | سپری کردن زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | فشار زمانی | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | برش‌کاران و پرداخت‌کاران دستی | تیزاب‌کاران و حکاکان | طراحان مد | کارگران چیدمان فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین کفش‌دوزی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | خیاطان، لباس‌دوزان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | ابزارسازان و قالب‌سازان</t>
+          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | برش‌دهندگان و پرداخت‌کاران دستی | حکاکان و تیزاب‌کاران | طراحان مد | کارگران شابلون‌زنی، فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سازندگان ابزار و قالب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | پایش | یادگیری فعال | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دست | چالاکی انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | تشخیص رنگ‌های بصری | تجسم | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری گسترده | قدرت تنه | ترتیب‌دهی اطلاعات | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | اصالت | بیان شفاهی | درک شفاهی | وضوح گفتار | درک عمق</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | تشخیص رنگ بصری | تجسم | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ترتیب‌دهی اطلاعات | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | اصالت | بیان شفاهی | درک شفاهی | وضوح گفتار | درک عمق</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>سپری کردن زمان با استفاده از دست‌ها برای جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سپری کردن زمان در حالت ایستاده | اهمیت دقیق یا درست بودن | سپری کردن زمان برای انجام حرکات تکراری | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | سپری کردن زمان برای خم کردن یا چرخاندن بدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | داخل ساختمان، با کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌ها</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکاران بدنه خودرو و موارد مرتبط | کابینت‌سازان و نجاران نیمکت | نجاران | نصابان موکت | برش‌کاران و پرداخت‌کاران دستی | لایه‌سازان و سازندگان فایبرگلاس | پرداخت‌کاران مبلمان | کارگران سنباده‌زنی و پولیش‌کاری دستی | کارگران چیدمان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | دوزندگان دستی | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین کفش‌دوزی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | کابینت‌سازان و نجاران نیمکت | نجّاران | نصّابان موکت و فرش | برش‌دهندگان و پرداخت‌کاران دستی | لمینت‌کاران و سازندگان فایبرگلاس | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | کارگران شابلون‌زنی، فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | دوزندگان دستی | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی برنامه‌پذیر PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی مواد مورد نیاز MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP | Adobe Illustrator</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP | Adobe Illustrator</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>داخل ساختمان، بدون کنترل شرایط محیطی | سپری کردن زمان در حالت ایستاده | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سپری کردن زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سپری کردن زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | میزان اتوماسیون | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا کمک به یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین دوخت | دوزندگان دستی | خیاطان، لباس‌دوزان و دوزندگان سفارشی | روکوبان | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین کفش‌دوزی | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارگران خشک‌شویی و لباس‌شویی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | اپراتورها و متصدیان ماشین سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | الگوسازان پارچه و پوشاک | برش‌کاران و پرداخت‌کاران دستی | بازرسان، تست‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | طراحان مد | سرپرستان خط اول کارگران تولیدی و عملیاتی | کمک‌کارگران--کارگران تولیدی | کارگران تولیدی، سایر</t>
+          <t>اپراتورهای چرخ خیاطی | دوزندگان دستی | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | روکوبان | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | اتوکاران منسوجات، پوشاک و مواد مرتبط | کارکنان خشک‌شویی و لباس‌شویی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بافندگی منسوجات | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | الگوسازان پارچه و پوشاک | برش‌دهندگان و پرداخت‌کاران دستی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | طراحان مد | سرپرستان رده اول کارگران تولید و بهره‌برداری | کمک‌کاران--کارگران تولید | کارگران تولید، سایر موارد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دست | چالاکی انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | قدرت تنه | تجسم | زمان عکس‌العمل | قدرت ایستا | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت شنوایی | درک عمق | بینایی دور | انعطاف‌پذیری گسترده | جهت‌گیری پاسخ | تشخیص گفتار | توجه شنیداری</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | قدرت تنه | تجسم | زمان عکس‌العمل | قدرت ایستا | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت شنوایی | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سپری کردن زمان در حالت ایستاده | داخل ساختمان، بدون کنترل شرایط محیطی | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | فشار زمانی | ارتباط با دیگران | کار با یا کمک به یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | دفعات تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجاران | پرداخت‌کاران مبلمان | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | کمک‌نجاران | کارگران چیدمان فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اره‌کاری چوب | کارگران ورق‌کار فلز | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | ابزارسازان و قالب‌سازان | روکوبان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | دستیاران--نجاران | کارگران شابلون‌زنی، فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | کارگران ورق‌کاری | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | روکوبان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعال | تفکر انتقادی | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | تشخیص رنگ‌های بصری | ثبات دست و بازو | چالاکی دست | دقت کنترل | تجسم | قدرت تنه | توجه انتخابی | قدرت ایستا | قدرت پویا | هماهنگی چند عضو | چالاکی انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور</t>
+          <t>بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | مهارت دستی | دقت کنترل | تجسم | قدرت تنه | توجه انتخابی | قدرت ایستا | قدرت پویا | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | سپری کردن زمان در حالت ایستاده | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارگران | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا کمک به یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سپری کردن زمان برای انجام حرکات تکراری | سپری کردن زمان در حال راه رفتن یا دویدن | دفعات تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران نیمکت | نصابان موکت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | برش‌کاران و پرداخت‌کاران دستی | نصابان دیوار خشک و تایل سقف | لایه‌سازان و سازندگان فایبرگلاس | کف‌سازان، به جز موکت، چوب و تایل‌های سخت | سنباده‌زنان و پرداخت‌کاران کف | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | نقاشان، ساختمان و نگهداری | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | کارگران و پرداخت‌کاران موزاییک درجا (ترازو) | نصابان تایل و سنگ | روکوبان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>کابینت‌سازان و نجاران نیمکت | نصّابان موکت و فرش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | روکوبان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | سخن‌گفتن | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | امور اداری و مدیریت | مکانیک</t>
+          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | چالاکی دست | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | درک کتبی | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | زمان عکس‌العمل | توجه انتخابی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | درک کتبی | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | زمان عکس‌العمل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | سپری کردن زمان در حالت ایستاده | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سپری کردن زمان با استفاده از دست‌ها برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | دفعات تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارگران | کار با یا کمک به یک گروه کاری یا تیم</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کابینت‌سازان و نجاران نیمکت | نجاران | مونتاژکنندگان موتور و سایر ماشین‌ها | الگوسازان پارچه و پوشاک | پرداخت‌کاران مبلمان | کارگران سنباده‌زنی و پولیش‌کاری دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | کارگران چیدمان فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین فرز و رنده فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | الگوسازان فلز و پلاستیک | الگوسازان چوب | کارگران ورق‌کار فلز | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کابینت‌سازان و نجاران نیمکت | نجّاران | مونتاژکاران موتور و سایر ماشین‌آلات | الگوسازان پارچه و پوشاک | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | کارگران ورق‌کاری | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0089_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0089_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | مرتب‌سازی اطلاعات | چابکی دستی | توجه شنیداری | دید نزدیک | قدرت بالاتنه | قدرت ایستا | زمان واکنش | هماهنگی اندام‌ها | دقت کنترل | چابکی انگشتان | توجه انتخابی | حساسیت به مسئله | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | تجسم فضایی | وضوح گفتار | درک عمق | کنترل نرخ | جهت‌یابی پاسخ</t>
+          <t>ثبات دست و بازو | ترتیب‌دهی اطلاعات | مهارت دستی | توجه شنیداری | بینایی نزدیک | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | توجه انتخابی | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | تجسم | وضوح گفتار | درک عمق | کنترل نرخ | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و مراقبان دستگاه‌های اتصال چسبی | برشکاران و پیراستاران دستی | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های فرزکاری و رنده‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید مصنوعات کاغذی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اره‌کشی چوب | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی انگشتان | دقت کنترل | هماهنگی اندام‌ها | چابکی دستی | قدرت بالاتنه | دید نزدیک | توجه انتخابی | حساسیت به مسئله | درک شفاهی | توجه شنیداری | زمان واکنش | تجسم فضایی | بیان شفاهی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | قدرت تنه | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله | درک شفاهی | توجه شنیداری | زمان عکس‌العمل | تجسم | بیان شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و مراقبان دستگاه‌های اتصال چسبی | برشکاران و پیراستاران دستی | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید مصنوعات کاغذی | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های نورد فلز و پلاستیک | دوزندگان دستی | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | دقت کنترل | چابکی انگشتان | چابکی دستی | زمان واکنش | هماهنگی اندام‌ها | قدرت بالاتنه | دید نزدیک | انعطاف‌پذیری بدنی | قدرت ایستا | توجه انتخابی | حساسیت به مسئله | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | انعطاف‌پذیری در طبقه‌بندی | بیان شفاهی | وضوح گفتار | توجه شنیداری | تشخیص رنگ | دید دور | سرعت مچ و انگشتان | کنترل نرخ</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | زمان عکس‌العمل | هماهنگی چند عضو | قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | توجه انتخابی | حساسیت به مسئله | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | وضوح گفتار | توجه شنیداری | تشخیص رنگ بصری | بینایی دور | سرعت مچ و انگشتان | کنترل نرخ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و مراقبان دستگاه‌های اتصال چسبی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران کلاف | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های فرزکاری و رنده‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید مصنوعات کاغذی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های نورد فلز و پلاستیک | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | ریاضیات | آموزش و یاددهی | مکانیک</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ریاضیات | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | دید نزدیک | چابکی انگشتان | استواری دست و بازو | درک شفاهی | چابکی دستی | هماهنگی اندام‌ها | زمان واکنش | کنترل نرخ | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت بالاتنه | تقسیم توجه | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | انعطاف‌پذیری در طبقه‌بندی | درک کتبی | وضوح گفتار | توجه شنیداری</t>
+          <t>حساسیت به مسئله | دقت کنترل | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | درک شفاهی | مهارت دستی | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | تقسیم توجه | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | درک کتبی | وضوح گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و مراقبان دستگاه‌های اتصال چسبی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران کلاف | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های فرزکاری و رنده‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های ابزار چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید مصنوعات کاغذی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های نورد فلز و پلاستیک | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری سخت و نرم | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | آموزش و یاددهی</t>
+          <t>طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | ابتکار و اصالت | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال ریاضی | درک کتبی | بیان شفاهی | چابکی انگشتان | مهارت محاسبات عددی | درک شفاهی | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | سرعت ادراک | توجه انتخابی | روانی ایده‌ها | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | دید دور | چابکی دستی | استواری دست و بازو | انعطاف‌پذیری در بستن الگوها | بیان کتبی | تشخیص رنگ | دقت کنترل | تقسیم توجه</t>
+          <t>تجسم | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال ریاضی | درک کتبی | بیان شفاهی | مهارت انگشتان | توانایی عددی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | سرعت ادراکی | توجه انتخابی | روانی ایده‌ها | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | بینایی دور | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | برشکاران و پیراستاران دستی | قلم‌زنان و حکاکان | طراحان مد و لباس | نشانه‌گذاران و خط‌کشان فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان سنگ در تولید | خیاطان، دوزندگان زنانه و سفارشی‌دوزان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | قالب‌سازان و ابزارسازان</t>
+          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | برشکاران و پیرایشگران دستی | حکاکان و اسیدکاران | طراحان مد و پوشاک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | هماهنگی اندام‌ها | تشخیص رنگ | تجسم فضایی | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری بدنی | قدرت بالاتنه | مرتب‌سازی اطلاعات | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری در بستن الگوها | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | ابتکار و اصالت | بیان شفاهی | درک شفاهی | وضوح گفتار | درک عمق</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | تشخیص رنگ بصری | تجسم | درک کتبی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ترتیب‌دهی اطلاعات | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | اصالت | بیان شفاهی | درک شفاهی | وضوح گفتار | درک عمق</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | صافکاران و تعمیرکاران بدنه خودرو | کابینت‌سازان و نجاران کارگاهی | نجاران عمومی | نصابان موکت و کف‌پوش | برشکاران و پیراستاران دستی | لایه‌نشینان و سازندگان فایبرگلاس | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کارگران سنگ‌زنی و پرداخت‌کاری دستی | نشانه‌گذاران و خط‌کشان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | دوزندگان دستی | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان سنگ در تولید | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | موکت‌کاران و نصابان فرش | برشکاران و پیرایشگران دستی | لایه‌نشانان و سازندگان فایبرگلاس | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی | شیمی</t>
+          <t>تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | شیمی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | استواری دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>چرخکاران و دوزندگان صنعتی | دوزندگان دستی | خیاطان، دوزندگان زنانه و سفارشی‌دوزان | رویه‌کوبان و مبل‌کوبان | کارگران و تعمیرکاران کفش و چرم | اپراتورها و مراقبان ماشین‌آلات کفاشی | اتوکاران و پرس‌کاران منسوجات و پوشاک | کارگران لباسشویی و خشکشویی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | الگوسازان پارچه و پوشاک | برشکاران و پیراستاران دستی | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و توزین‌گران | طراحان مد و لباس | سرپرستان رده‌اول کارگران تولید و عملیات | کارگران کمکی خطوط تولید | کارگران تولید، سایر مشاغل</t>
+          <t>چرخکاران صنعتی | دوزندگان دستی | خیاطان و دوزندگان سفارشی | رویه‌کوبان و مبل‌کوبان | کارگران و تعمیرکاران کفش و چرم | اپراتورها و متصدیان ماشین‌آلات کفش | اتوکاران منسوجات، پوشاک و مواد وابسته | کارگران خشکشویی و رختشویخانه | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | الگوسازان پارچه و پوشاک | برشکاران و پیرایشگران دستی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | طراحان مد و پوشاک | سرپرستان رده اول کارگران تولید و عملیات | کمک‌کارگران خطوط تولید | سایر کارگران خطوط تولید</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار برآورد و متره رایانه‌ای | سیستم مدیریت نگهداری و تعمیرات رایانه‌ای CMMS | Microsoft Excel | Microsoft Outlook | Microsoft Windows</t>
+          <t>Autodesk AutoCAD | نرم‌افزار برآورد و متره رایانه‌ای | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Outlook | Microsoft Windows</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | هماهنگی اندام‌ها | قدرت بالاتنه | تجسم فضایی | زمان واکنش | قدرت ایستا | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی | سرعت ادراک | انعفاط‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت شنوایی | درک عمق | دید دور | انعطاف‌پذیری بدنی | جهت‌یابی پاسخ | تشخیص گفتار | توجه شنیداری</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | قدرت تنه | تجسم | زمان عکس‌العمل | قدرت ایستا | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت شنوایی | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان فلزی | نجاران عمومی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | کارگران کمکی نجاران | نشانه‌گذاران و خط‌کشان فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اره‌کشی چوب | ورق‌کاران و فلزکاران | سنگ‌تراشان و حکاکان سنگ در تولید | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان | رویه‌کوبان و مبل‌کوبان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | کمک‌نجاران | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | کارگران ورق‌کاری فلزی | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | رویه‌کوبان و مبل‌کوبان | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص رنگ | استواری دست و بازو | چابکی دستی | دقت کنترل | تجسم فضایی | قدرت بالاتنه | توجه انتخابی | قدرت ایستا | قدرت پویا | هماهنگی اندام‌ها | چابکی انگشتان | انعطاف‌پذیری در بستن الگوها | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | سرعت ادراک | مرتب‌سازی اطلاعات | تشخیص گفتار | دید دور</t>
+          <t>بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | مهارت دستی | دقت کنترل | تجسم | قدرت تنه | توجه انتخابی | قدرت ایستا | قدرت پویا | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | نصابان موکت و کف‌پوش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و پاشش | برشکاران و پیراستاران دستی | نصابان صفحات گچی و تایل سقف | لایه‌نشینان و سازندگان فایبرگلاس | نصابان کف‌پوش به‌جز فرش، موکت، چوب و کاشی سخت | سنباده‌زنان و پرداخت‌کاران پارکت و کف چوبی | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | نقاشان ساختمان و تاسیسات | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان سنگ در تولید | سازندگان و مونتاژکاران سازه‌های فلزی | کارگران و پرداخت‌کاران موزاییک و ترازو | کاشی‌کاران و سنگ‌کاران ساختمانی | رویه‌کوبان و مبل‌کوبان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | موکت‌کاران و نصابان فرش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران و پیرایشگران دستی | نصابان دیوار کاذب و تایل سقف | لایه‌نشانان و سازندگان فایبرگلاس | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | رویه‌کوبان و مبل‌کوبان | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری | مکانیک</t>
+          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | استواری دست و بازو | چابکی انگشتان | دقت کنترل | چابکی دستی | تجسم فضایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک شفاهی | درک کتبی | هماهنگی اندام‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | بیان شفاهی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | زمان واکنش | توجه انتخابی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | درک کتبی | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | زمان عکس‌العمل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کابینت‌سازان و نجاران کارگاهی | نجاران عمومی | مونتاژکاران موتور و ماشین‌آلات | الگوسازان پارچه و پوشاک | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | نشانه‌گذاران و خط‌کشان فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های فرزکاری و رنده‌کاری فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | ورق‌کاران و فلزکاران | سنگ‌تراشان و حکاکان سنگ در تولید | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | مونتاژکاران موتور و سایر ماشین‌آلات | الگوسازان پارچه و پوشاک | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | الگوسازان چوب | کارگران ورق‌کاری فلزی | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
